--- a/import-templates/import-template-assets.xlsx
+++ b/import-templates/import-template-assets.xlsx
@@ -50,7 +50,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -72,6 +72,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F4F6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB45309"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -103,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -127,6 +133,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -638,7 +647,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">หัวคอลัมน์สีส้ม = จำเป็นต้องกรอก / สีเขียว = ไม่บังคับ (เว้นว่างได้)</t>
+          <t xml:space="preserve">หัวคอลัมน์สีส้ม = จำเป็นต้องกรอก / สีเหลือง = ไม่บังคับ แต่แนะนำอย่างยิ่ง / สีเขียว = เว้นว่างได้</t>
         </is>
       </c>
     </row>

--- a/import-templates/import-template-assets.xlsx
+++ b/import-templates/import-template-assets.xlsx
@@ -349,7 +349,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">โรงงานบางปู เฟส 2</t>
+          <t xml:space="preserve">PT บางปู สมุทรปราการ</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -413,12 +413,12 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">โรงงานบางปู เฟส 2</t>
+          <t xml:space="preserve">PT บางปู สมุทรปราการ</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">แผงโซลาร์ ชุดหลังคา A</t>
+          <t xml:space="preserve">ตู้เติมลมโครงเหล็ก-Outdoor</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -428,22 +428,18 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">solar_panel</t>
+          <t xml:space="preserve">other</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jinko</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JKM580N-72HL4</t>
-        </is>
-      </c>
+          <t xml:space="preserve">G5</t>
+        </is>
+      </c>
+      <c r="F3" s="9"/>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">JK24A0099123</t>
+          <t xml:space="preserve">6972220250521</t>
         </is>
       </c>
       <c r="H3" s="9"/>
@@ -464,7 +460,7 @@
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">144</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="M3" s="9" t="inlineStr">
@@ -474,7 +470,7 @@
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">รวม 320 แผง</t>
+          <t xml:space="preserve">ประเภทที่ไม่เข้าพวกให้ใช้ other</t>
         </is>
       </c>
     </row>
@@ -530,14 +526,14 @@
       </c>
       <c r="N4" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">โครงการเฟสแรก</t>
+          <t xml:space="preserve">asset_type = project จึงกรอก project_number แทน serial_number</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">สาขาระยอง (หลังคาอาคาร A)</t>
+          <t xml:space="preserve">สาขาระยอง (อาคาร A)</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">

--- a/import-templates/import-template-assets.xlsx
+++ b/import-templates/import-template-assets.xlsx
@@ -146,23 +146,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1" style="3"/>
-    <col min="11" max="11" width="16" customWidth="1" style="3"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1" style="3"/>
+    <col min="12" max="12" width="16" customWidth="1" style="3"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -176,77 +177,82 @@
           <t xml:space="preserve">name</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asset_tag</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">asset_type</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">brand</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">model</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">serial_number</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">project_number</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">group_name</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">install_date</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">warranty_start</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">warranty_months</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:O1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="C2:C2000">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="D2:D2000">
       <formula1>"object,project"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="D2:D2000">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="E2:E2000">
       <formula1>"solar_panel,inverter,ev_charger,battery,meter,other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="M2:M2000">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="N2:N2000">
       <formula1>"operational,degraded,down,retired"</formula1>
     </dataValidation>
   </dataValidations>
@@ -255,23 +261,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -285,62 +292,67 @@
           <t xml:space="preserve">name</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asset_tag</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">asset_type</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">brand</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">model</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">serial_number</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">project_number</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">group_name</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">install_date</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">warranty_start</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">warranty_months</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
@@ -359,56 +371,61 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">INV-001</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">object</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">inverter</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Huawei</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">SUN2000-100KTL-M1</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">HV2340019876</t>
         </is>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="9"/>
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">อาคาร A</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">60</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="N2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">operational</t>
         </is>
       </c>
-      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -423,52 +440,57 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">AIR-014</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">object</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">other</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">G5</t>
         </is>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="9"/>
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">6972220250521</t>
         </is>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="9"/>
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">อาคาร A</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">24</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">operational</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">ประเภทที่ไม่เข้าพวกให้ใช้ other</t>
         </is>
@@ -485,46 +507,47 @@
           <t xml:space="preserve">โครงการติดตั้งโซลาร์ 1.2 MW</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">project</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">other</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="9"/>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">PRJ-2024-0087</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="9"/>
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-11-01</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-11-01</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">60</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="N4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">operational</t>
         </is>
       </c>
-      <c r="N4" s="9" t="inlineStr">
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">asset_type = project จึงกรอก project_number แทน serial_number</t>
         </is>
@@ -543,52 +566,57 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">EV-003</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">object</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">ev_charger</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Delta</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">AC Max 22kW</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">DL2412000455</t>
         </is>
       </c>
-      <c r="H5" s="9"/>
       <c r="I5" s="9"/>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J5" s="9"/>
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-02-20</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-02-20</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">24</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">degraded</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">จอแสดงผลมีปัญหา รอเปลี่ยนอะไหล่</t>
         </is>
@@ -608,7 +636,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -765,22 +793,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">asset_type</t>
+          <t xml:space="preserve">asset_tag</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใช่</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตัวเลือก: object / project</t>
+          <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">object = อุปกรณ์ชิ้นจริง ระบุด้วย serial_number · project = โครงการ ระบุด้วย project_number</t>
+          <t xml:space="preserve">เลขครุภัณฑ์ / QR Code ที่ติดอยู่บนเครื่อง เช่น Shell-001 — คนละอันกับรหัส Asset (AS-0001) ที่ระบบออกให้เอง</t>
         </is>
       </c>
     </row>
@@ -792,7 +820,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">asset_type</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -802,12 +830,12 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตัวเลือก: solar_panel / inverter / ev_charger / battery / meter / other</t>
+          <t xml:space="preserve">ตัวเลือก: object / project</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ประเภท: solar_panel = แผงโซลาร์, inverter = อินเวอร์เตอร์, ev_charger = ตู้ชาร์จ EV, battery = แบตเตอรี่, meter = มิเตอร์, other = อื่นๆ</t>
+          <t xml:space="preserve">object = อุปกรณ์ชิ้นจริง ระบุด้วย serial_number · project = โครงการ ระบุด้วย project_number</t>
         </is>
       </c>
     </row>
@@ -819,22 +847,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">ใช่</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ข้อความ</t>
+          <t xml:space="preserve">ตัวเลือก: solar_panel / inverter / ev_charger / battery / meter / other</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ยี่ห้อ เช่น Huawei, Growatt, Delta</t>
+          <t xml:space="preserve">ประเภท: solar_panel = แผงโซลาร์, inverter = อินเวอร์เตอร์, ev_charger = ตู้ชาร์จ EV, battery = แบตเตอรี่, meter = มิเตอร์, other = อื่นๆ</t>
         </is>
       </c>
     </row>
@@ -846,7 +874,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">model</t>
+          <t xml:space="preserve">brand</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -861,7 +889,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">รุ่น เช่น SUN2000-100KTL</t>
+          <t xml:space="preserve">ยี่ห้อ เช่น Huawei, Growatt, Delta</t>
         </is>
       </c>
     </row>
@@ -873,7 +901,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">serial_number</t>
+          <t xml:space="preserve">model</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -888,7 +916,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">S/N ของอุปกรณ์ — ใช้เฉพาะ asset_type = object (ไม่บังคับให้ไม่ซ้ำ เพราะคนละยี่ห้อ S/N ซ้ำกันได้)</t>
+          <t xml:space="preserve">รุ่น เช่น SUN2000-100KTL</t>
         </is>
       </c>
     </row>
@@ -900,7 +928,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">project_number</t>
+          <t xml:space="preserve">serial_number</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -915,7 +943,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">เลขที่โครงการ — ใช้เฉพาะ asset_type = project</t>
+          <t xml:space="preserve">S/N ของอุปกรณ์ — ใช้เฉพาะ asset_type = object (ไม่บังคับให้ไม่ซ้ำ เพราะคนละยี่ห้อ S/N ซ้ำกันได้)</t>
         </is>
       </c>
     </row>
@@ -927,7 +955,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">group_name</t>
+          <t xml:space="preserve">project_number</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -942,7 +970,7 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชื่อกลุ่ม Asset ภายในไซต์ เช่น “อาคาร A” — ถ้ายังไม่มีกลุ่มนี้ในไซต์ ระบบจะไม่ผูกให้</t>
+          <t xml:space="preserve">เลขที่โครงการ — ใช้เฉพาะ asset_type = project</t>
         </is>
       </c>
     </row>
@@ -954,7 +982,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">install_date</t>
+          <t xml:space="preserve">group_name</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -964,12 +992,12 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">วันที่ YYYY-MM-DD</t>
+          <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">วันที่ติดตั้ง</t>
+          <t xml:space="preserve">ชื่อกลุ่ม Asset ภายในไซต์ เช่น “อาคาร A” — ถ้ายังไม่มีกลุ่มนี้ในไซต์ ระบบจะไม่ผูกให้</t>
         </is>
       </c>
     </row>
@@ -981,7 +1009,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">warranty_start</t>
+          <t xml:space="preserve">install_date</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -996,7 +1024,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">วันที่เริ่มประกัน (ถ้าเว้นว่างจะไม่คำนวณวันหมดประกันให้)</t>
+          <t xml:space="preserve">วันที่ติดตั้ง</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1036,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">warranty_months</t>
+          <t xml:space="preserve">warranty_start</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1018,12 +1046,12 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">จำนวนเต็ม</t>
+          <t xml:space="preserve">วันที่ YYYY-MM-DD</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">อายุประกันเป็นเดือน เช่น 60 = 5 ปี — วันหมดประกันคำนวณจาก warranty_start + จำนวนเดือนนี้</t>
+          <t xml:space="preserve">วันที่เริ่มประกัน (ถ้าเว้นว่างจะไม่คำนวณวันหมดประกันให้)</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1063,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">warranty_months</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1045,12 +1073,12 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตัวเลือก: operational / degraded / down / retired</t>
+          <t xml:space="preserve">จำนวนเต็ม</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">สถานะเครื่อง: operational = ใช้งานได้, degraded = พอใช้งานได้, down = ใช้งานไม่ได้, retired = ปลดระวาง · เว้นว่าง = operational</t>
+          <t xml:space="preserve">อายุประกันเป็นเดือน เช่น 60 = 5 ปี — วันหมดประกันคำนวณจาก warranty_start + จำนวนเดือนนี้</t>
         </is>
       </c>
     </row>
@@ -1062,20 +1090,47 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ตัวเลือก: operational / degraded / down / retired</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">สถานะเครื่อง: operational = ใช้งานได้, degraded = พอใช้งานได้, down = ใช้งานไม่ได้, retired = ปลดระวาง · เว้นว่าง = operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">notes</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">หมายเหตุ</t>
         </is>

--- a/import-templates/import-template-assets.xlsx
+++ b/import-templates/import-template-assets.xlsx
@@ -146,24 +146,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1" style="3"/>
-    <col min="12" max="12" width="16" customWidth="1" style="3"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="30" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1" style="3"/>
+    <col min="13" max="13" width="16" customWidth="1" style="3"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -172,87 +173,89 @@
           <t xml:space="preserve">site_name</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">asset_tag</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">asset_type</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">brand</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">model</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">serial_number</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">project_number</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">group_name</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">install_date</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">warranty_start</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">warranty_months</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">status</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="D2:D2000">
+  <autoFilter ref="A1:P1"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="E2:E2000">
       <formula1>"object,project"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="E2:E2000">
-      <formula1>"solar_panel,inverter,ev_charger,battery,meter,other"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="N2:N2000">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="O2:O2000">
       <formula1>"operational,degraded,down,retired"</formula1>
     </dataValidation>
   </dataValidations>
@@ -261,24 +264,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="30" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -287,72 +291,77 @@
           <t xml:space="preserve">site_name</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">asset_tag</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">asset_type</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">brand</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">model</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">serial_number</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">project_number</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">group_name</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">install_date</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">warranty_start</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">warranty_months</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">status</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
@@ -366,66 +375,71 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">บริษัท ไทยรุ่งเรือง ปิโตรเลียม จำกัด</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">อินเวอร์เตอร์ตัวที่ 1</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">INV-001</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">object</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">inverter</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Huawei</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">SUN2000-100KTL-M1</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">HV2340019876</t>
         </is>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="9"/>
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">อาคาร A</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="N2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">60</t>
         </is>
       </c>
-      <c r="N2" s="9" t="inlineStr">
+      <c r="O2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">operational</t>
         </is>
       </c>
-      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -435,62 +449,67 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">บริษัท ไทยรุ่งเรือง ปิโตรเลียม จำกัด</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">ตู้เติมลมโครงเหล็ก-Outdoor</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">AIR-014</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">object</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">other</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">G5</t>
         </is>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="9"/>
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">6972220250521</t>
         </is>
       </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="9"/>
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">อาคาร A</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">24</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">operational</t>
         </is>
       </c>
-      <c r="O3" s="9" t="inlineStr">
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">ประเภทที่ไม่เข้าพวกให้ใช้ other</t>
         </is>
@@ -504,50 +523,55 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">ห้างหุ้นส่วนจำกัด เอ็นเนอร์ยี่ พลัส</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">โครงการติดตั้งโซลาร์ 1.2 MW</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="9"/>
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">project</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">other</t>
         </is>
       </c>
-      <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="9"/>
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">PRJ-2024-0087</t>
         </is>
       </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="9"/>
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-11-01</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-11-01</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="N4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">60</t>
         </is>
       </c>
-      <c r="N4" s="9" t="inlineStr">
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">operational</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="P4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">asset_type = project จึงกรอก project_number แทน serial_number</t>
         </is>
@@ -561,62 +585,67 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">บริษัท สุขสบาย เซอร์วิส จำกัด</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">ตู้ชาร์จ EV จุดที่ 3</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">EV-003</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">object</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">ev_charger</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Delta</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">AC Max 22kW</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">DL2412000455</t>
         </is>
       </c>
-      <c r="I5" s="9"/>
       <c r="J5" s="9"/>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="9"/>
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-02-20</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-02-20</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">24</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">degraded</t>
         </is>
       </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="P5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">จอแสดงผลมีปัญหา รอเปลี่ยนอะไหล่</t>
         </is>
@@ -636,7 +665,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -766,12 +795,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">company_name</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใช่</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -781,7 +810,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชื่อ Asset เช่น “อินเวอร์เตอร์ตัวที่ 1” หรือชื่อโครงการ</t>
+          <t xml:space="preserve">ชื่อลูกค้าเจ้าของไซต์ — จำเป็นเมื่อมีไซต์ชื่อซ้ำกันหลายราย (เช่น “ระยอง” มี 9 แห่งคนละลูกค้า) ถ้าชื่อไซต์ไม่ซ้ำจะเว้นว่างได้</t>
         </is>
       </c>
     </row>
@@ -793,12 +822,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">asset_tag</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">ใช่</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -808,7 +837,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">เลขครุภัณฑ์ / QR Code ที่ติดอยู่บนเครื่อง เช่น Shell-001 — คนละอันกับรหัส Asset (AS-0001) ที่ระบบออกให้เอง</t>
+          <t xml:space="preserve">ชื่อ Asset เช่น “อินเวอร์เตอร์ตัวที่ 1” หรือชื่อโครงการ</t>
         </is>
       </c>
     </row>
@@ -820,22 +849,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">asset_type</t>
+          <t xml:space="preserve">asset_tag</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใช่</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตัวเลือก: object / project</t>
+          <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">object = อุปกรณ์ชิ้นจริง ระบุด้วย serial_number · project = โครงการ ระบุด้วย project_number</t>
+          <t xml:space="preserve">เลขครุภัณฑ์ / QR Code ที่ติดอยู่บนเครื่อง เช่น Shell-001 — คนละอันกับรหัส Asset (AS-0001) ที่ระบบออกให้เอง</t>
         </is>
       </c>
     </row>
@@ -847,7 +876,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">asset_type</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -857,12 +886,12 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตัวเลือก: solar_panel / inverter / ev_charger / battery / meter / other</t>
+          <t xml:space="preserve">ตัวเลือก: object / project</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ประเภท: solar_panel = แผงโซลาร์, inverter = อินเวอร์เตอร์, ev_charger = ตู้ชาร์จ EV, battery = แบตเตอรี่, meter = มิเตอร์, other = อื่นๆ</t>
+          <t xml:space="preserve">object = อุปกรณ์ชิ้นจริง ระบุด้วย serial_number · project = โครงการ ระบุด้วย project_number</t>
         </is>
       </c>
     </row>
@@ -874,12 +903,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">ใช่</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -889,7 +918,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ยี่ห้อ เช่น Huawei, Growatt, Delta</t>
+          <t xml:space="preserve">ชนิดเครื่อง เช่น “Probe”, “Liquid Sensor”, “Nozzle (หัวฉีด)” — พิมพ์ได้อิสระ ไม่จำกัดตัวเลือก · ค่าที่ระบบมีคำแปลไทยให้: solar_panel = แผงโซลาร์, inverter = อินเวอร์เตอร์, ev_charger = ตู้ชาร์จ EV, battery = แบตเตอรี่, meter = มิเตอร์, other = อื่นๆ</t>
         </is>
       </c>
     </row>
@@ -901,7 +930,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">model</t>
+          <t xml:space="preserve">brand</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -916,7 +945,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">รุ่น เช่น SUN2000-100KTL</t>
+          <t xml:space="preserve">ยี่ห้อ เช่น Huawei, Growatt, Delta</t>
         </is>
       </c>
     </row>
@@ -928,7 +957,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">serial_number</t>
+          <t xml:space="preserve">model</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -943,7 +972,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">S/N ของอุปกรณ์ — ใช้เฉพาะ asset_type = object (ไม่บังคับให้ไม่ซ้ำ เพราะคนละยี่ห้อ S/N ซ้ำกันได้)</t>
+          <t xml:space="preserve">รุ่น เช่น SUN2000-100KTL</t>
         </is>
       </c>
     </row>
@@ -955,7 +984,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">project_number</t>
+          <t xml:space="preserve">serial_number</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -970,7 +999,7 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">เลขที่โครงการ — ใช้เฉพาะ asset_type = project</t>
+          <t xml:space="preserve">S/N ของอุปกรณ์ — ใช้เฉพาะ asset_type = object (ไม่บังคับให้ไม่ซ้ำ เพราะคนละยี่ห้อ S/N ซ้ำกันได้)</t>
         </is>
       </c>
     </row>
@@ -982,7 +1011,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">group_name</t>
+          <t xml:space="preserve">project_number</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -997,7 +1026,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชื่อกลุ่ม Asset ภายในไซต์ เช่น “อาคาร A” — ถ้ายังไม่มีกลุ่มนี้ในไซต์ ระบบจะไม่ผูกให้</t>
+          <t xml:space="preserve">เลขที่โครงการ — ใช้เฉพาะ asset_type = project</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1038,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">install_date</t>
+          <t xml:space="preserve">group_name</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1019,12 +1048,12 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">วันที่ YYYY-MM-DD</t>
+          <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">วันที่ติดตั้ง</t>
+          <t xml:space="preserve">ชื่อกลุ่ม Asset ภายในไซต์ เช่น “อาคาร A” — ถ้ายังไม่มีกลุ่มนี้ในไซต์ ระบบจะไม่ผูกให้</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1065,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">warranty_start</t>
+          <t xml:space="preserve">install_date</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1051,7 +1080,7 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">วันที่เริ่มประกัน (ถ้าเว้นว่างจะไม่คำนวณวันหมดประกันให้)</t>
+          <t xml:space="preserve">วันที่ติดตั้ง</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1092,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">warranty_months</t>
+          <t xml:space="preserve">warranty_start</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1073,12 +1102,12 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">จำนวนเต็ม</t>
+          <t xml:space="preserve">วันที่ YYYY-MM-DD</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">อายุประกันเป็นเดือน เช่น 60 = 5 ปี — วันหมดประกันคำนวณจาก warranty_start + จำนวนเดือนนี้</t>
+          <t xml:space="preserve">วันที่เริ่มประกัน (ถ้าเว้นว่างจะไม่คำนวณวันหมดประกันให้)</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1119,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">warranty_months</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1100,12 +1129,12 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตัวเลือก: operational / degraded / down / retired</t>
+          <t xml:space="preserve">จำนวนเต็ม</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">สถานะเครื่อง: operational = ใช้งานได้, degraded = พอใช้งานได้, down = ใช้งานไม่ได้, retired = ปลดระวาง · เว้นว่าง = operational</t>
+          <t xml:space="preserve">อายุประกันเป็นเดือน เช่น 60 = 5 ปี — วันหมดประกันคำนวณจาก warranty_start + จำนวนเดือนนี้</t>
         </is>
       </c>
     </row>
@@ -1117,20 +1146,47 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ตัวเลือก: operational / degraded / down / retired</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">สถานะเครื่อง: operational = ใช้งานได้, degraded = พอใช้งานได้, down = ใช้งานไม่ได้, retired = ปลดระวาง · เว้นว่าง = operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">notes</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">หมายเหตุ</t>
         </is>
